--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.55292903845654</v>
+        <v>3.664850968749187</v>
       </c>
       <c r="D2" t="n">
-        <v>34.57390318376972</v>
+        <v>5.618259267362579</v>
       </c>
       <c r="E2" t="n">
-        <v>9.501009956053073</v>
+        <v>1.543914117858624</v>
       </c>
       <c r="F2" t="n">
-        <v>3.672278865230065</v>
+        <v>0.5967453155998855</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.36614052724706</v>
+        <v>6.884497835677648</v>
       </c>
       <c r="D3" t="n">
-        <v>41.52892875647375</v>
+        <v>6.748450922926986</v>
       </c>
       <c r="E3" t="n">
-        <v>9.501009956053073</v>
+        <v>1.543914117858624</v>
       </c>
       <c r="F3" t="n">
-        <v>3.672278865230065</v>
+        <v>0.5967453155998855</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.03255912349969</v>
+        <v>6.9927908575687</v>
       </c>
       <c r="D4" t="n">
-        <v>42.99166482522448</v>
+        <v>6.986145534098979</v>
       </c>
       <c r="E4" t="n">
-        <v>9.501009956053073</v>
+        <v>1.543914117858624</v>
       </c>
       <c r="F4" t="n">
-        <v>3.672278865230065</v>
+        <v>0.5967453155998855</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
